--- a/data/Terre di Pedemonte/investment_decision/Verscio_SFH_2005-2014_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Verscio_SFH_2005-2014_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.195599282649442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>12840.45669930562</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.195599282649442</v>
       </c>
       <c r="G2" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.195599282649442</v>
       </c>
       <c r="I2" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.195599282649442</v>
       </c>
       <c r="K2" t="n">
         <v>12840.45669930562</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>24.56743633925909</v>
+        <v>20.34487661423043</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>12840.45669930562</v>
       </c>
       <c r="F3" t="n">
-        <v>27.37941428571431</v>
+        <v>20.75582607706176</v>
       </c>
       <c r="G3" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="H3" t="n">
-        <v>24.56743633925909</v>
+        <v>20.78565783036077</v>
       </c>
       <c r="I3" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="J3" t="n">
-        <v>27.37941428571431</v>
+        <v>20.97072531655805</v>
       </c>
       <c r="K3" t="n">
         <v>12840.45669930562</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>68.0298509594456</v>
+        <v>61.89612275050285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>12840.45669930562</v>
       </c>
       <c r="F4" t="n">
-        <v>71.20147285591494</v>
+        <v>61.91058528946999</v>
       </c>
       <c r="G4" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="H4" t="n">
-        <v>68.0298511151064</v>
+        <v>62.54087488239363</v>
       </c>
       <c r="I4" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="J4" t="n">
-        <v>71.20147285591494</v>
+        <v>61.91258997871434</v>
       </c>
       <c r="K4" t="n">
         <v>12840.45669930562</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>68.04949301195239</v>
+        <v>72.69093797966843</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>12840.45669930562</v>
       </c>
       <c r="F5" t="n">
-        <v>71.20147285591494</v>
+        <v>72.69093797966816</v>
       </c>
       <c r="G5" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="H5" t="n">
-        <v>68.23881920956194</v>
+        <v>72.55091104569119</v>
       </c>
       <c r="I5" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="J5" t="n">
-        <v>71.20147285591494</v>
+        <v>72.54635358617006</v>
       </c>
       <c r="K5" t="n">
         <v>12840.45669930562</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>68.95082053485494</v>
+        <v>72.69093797966843</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>12840.45669930562</v>
       </c>
       <c r="F6" t="n">
-        <v>71.20147285591494</v>
+        <v>72.69093797966816</v>
       </c>
       <c r="G6" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="H6" t="n">
-        <v>68.95082053485494</v>
+        <v>72.55091104569119</v>
       </c>
       <c r="I6" t="n">
         <v>12840.45669930562</v>
       </c>
       <c r="J6" t="n">
-        <v>71.20147285591494</v>
+        <v>72.54635358617004</v>
       </c>
       <c r="K6" t="n">
         <v>12840.45669930562</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>19.26068504895843</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10.96817986681314</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>19.26068504895843</v>
+        <v>20.60175899912409</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>10.96817986681314</v>
+        <v>20.60175899912409</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>19.26068504895843</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>13.35139152087324</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>19.26068504895843</v>
+        <v>25.07819471927569</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>13.35139152087324</v>
+        <v>25.07819471927569</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>19.26068504895843</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>14.3276268858201</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>19.26068504895843</v>
+        <v>26.91187778786864</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>14.3276268858201</v>
+        <v>26.91187778786864</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>19.26068504895843</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>14.84946936388703</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>19.26068504895843</v>
+        <v>27.89206530295215</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>14.84946936388703</v>
+        <v>27.89206530295215</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>19.26068504895843</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>15.1755536237313</v>
+        <v>36.17774292134831</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>19.26068504895843</v>
+        <v>28.504556109658</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>15.1755536237313</v>
+        <v>28.504556109658</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004870314635294118</v>
+        <v>0.002435157317647059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004870314635294118</v>
+        <v>0.002119794870645249</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004870314635294118</v>
+        <v>0.002435157317647059</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004870314635294118</v>
+        <v>0.002114452932242145</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.005600861830588236</v>
+        <v>0.003652735976470588</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005600861830588235</v>
+        <v>0.003652735976470588</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005600861830588235</v>
+        <v>0.003652735976470588</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005600861830588235</v>
+        <v>0.003652735976470588</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.005600861830588235</v>
+        <v>0.004397423216605841</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004383283171764706</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626926969402059</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005844377562352942</v>
+        <v>0.004626798903529412</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>2.363561045</v>
+        <v>1.594866548821853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>4.346755812</v>
       </c>
       <c r="F19" t="n">
-        <v>2.363561045</v>
+        <v>1.595102467255906</v>
       </c>
       <c r="G19" t="n">
         <v>4.346755812</v>
       </c>
       <c r="H19" t="n">
-        <v>2.363561045</v>
+        <v>1.336905237847064</v>
       </c>
       <c r="I19" t="n">
         <v>4.346755812</v>
       </c>
       <c r="J19" t="n">
-        <v>2.363561045</v>
+        <v>1.328687219994844</v>
       </c>
       <c r="K19" t="n">
         <v>4.346755812</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>2.444574450427533</v>
+        <v>1.660148722355731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>4.346755812</v>
       </c>
       <c r="F20" t="n">
-        <v>2.506321026373122</v>
+        <v>1.660384640789784</v>
       </c>
       <c r="G20" t="n">
         <v>4.346755812</v>
       </c>
       <c r="H20" t="n">
-        <v>2.444574450427533</v>
+        <v>1.402187411380942</v>
       </c>
       <c r="I20" t="n">
         <v>4.346755812</v>
       </c>
       <c r="J20" t="n">
-        <v>2.506321026373122</v>
+        <v>1.393969393528721</v>
       </c>
       <c r="K20" t="n">
         <v>4.346755812</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>2.444574450427533</v>
+        <v>1.660148722355731</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>4.346755812</v>
       </c>
       <c r="F21" t="n">
-        <v>2.506321026373122</v>
+        <v>1.660384640789784</v>
       </c>
       <c r="G21" t="n">
         <v>4.346755812</v>
       </c>
       <c r="H21" t="n">
-        <v>2.444574450427533</v>
+        <v>1.402187411380942</v>
       </c>
       <c r="I21" t="n">
         <v>4.346755812</v>
       </c>
       <c r="J21" t="n">
-        <v>2.506321026373122</v>
+        <v>1.393969393528721</v>
       </c>
       <c r="K21" t="n">
         <v>4.346755812</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.7686944961781471</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>4.346755812</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.7684585777440942</v>
       </c>
       <c r="G29" t="n">
         <v>4.346755812</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.026655807152935</v>
       </c>
       <c r="I29" t="n">
         <v>4.346755812</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.034873825005156</v>
       </c>
       <c r="K29" t="n">
         <v>4.346755812</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.7686944961781471</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>4.346755812</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.7684585777440942</v>
       </c>
       <c r="G30" t="n">
         <v>4.346755812</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.026655807152935</v>
       </c>
       <c r="I30" t="n">
         <v>4.346755812</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.034873825005156</v>
       </c>
       <c r="K30" t="n">
         <v>4.346755812</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.7686944961781471</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>4.346755812</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.7684585777440942</v>
       </c>
       <c r="G31" t="n">
         <v>4.346755812</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.026655807152935</v>
       </c>
       <c r="I31" t="n">
         <v>4.346755812</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.034873825005156</v>
       </c>
       <c r="K31" t="n">
         <v>4.346755812</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>44.13685146594736</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>25.59164847922444</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>44.13685146594736</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>44.13685146594736</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>31.11530206538852</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>44.13685146594736</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>44.13685146594736</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>33.39009724022183</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>44.13685146594736</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>44.13685146594736</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>34.62322190876719</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>44.13685146594736</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>44.13685146594736</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>35.40687570082634</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>44.13685146594736</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>6.513938399933015</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2399,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>8.568976181035385</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>4.730511988066504</v>
+        <v>4.708735018968106</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>20.76122989635906</v>
       </c>
       <c r="F54" t="n">
-        <v>4.679676274406388</v>
+        <v>4.18190210218273</v>
       </c>
       <c r="G54" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.709780575162361</v>
+      </c>
+      <c r="I54" t="n">
         <v>9.484802154335563</v>
       </c>
-      <c r="H54" t="n">
-        <v>4.238182072894745</v>
-      </c>
-      <c r="I54" t="n">
-        <v>20.76122989635906</v>
-      </c>
       <c r="J54" t="n">
-        <v>4.237946408634847</v>
+        <v>4.181894261049523</v>
       </c>
       <c r="K54" t="n">
         <v>9.484802154335563</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.116240915444117</v>
+        <v>5.141802103182967</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>20.76122989635906</v>
       </c>
       <c r="F55" t="n">
-        <v>5.116240915444117</v>
+        <v>4.753156967195836</v>
       </c>
       <c r="G55" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5.165986472150145</v>
+      </c>
+      <c r="I55" t="n">
         <v>9.979053545398589</v>
       </c>
-      <c r="H55" t="n">
-        <v>4.90525280674128</v>
-      </c>
-      <c r="I55" t="n">
-        <v>20.76122989635906</v>
-      </c>
       <c r="J55" t="n">
-        <v>4.892275835978231</v>
+        <v>4.752621154443459</v>
       </c>
       <c r="K55" t="n">
         <v>9.979053545398589</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.116240915444117</v>
+        <v>5.141802103182967</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>20.76122989635906</v>
       </c>
       <c r="F56" t="n">
-        <v>5.116240915444117</v>
+        <v>4.753156967195836</v>
       </c>
       <c r="G56" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5.165986472150145</v>
+      </c>
+      <c r="I56" t="n">
         <v>10.28415809404153</v>
       </c>
-      <c r="H56" t="n">
-        <v>4.90525280674128</v>
-      </c>
-      <c r="I56" t="n">
-        <v>20.76122989635906</v>
-      </c>
       <c r="J56" t="n">
-        <v>4.892275835978231</v>
+        <v>4.752621154443459</v>
       </c>
       <c r="K56" t="n">
         <v>10.28415809404153</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>6.513938399933015</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>8.568976181035385</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>9.484802154335563</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>9.979053545398589</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>20.76122989635906</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>10.28415809404153</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>20.76122989635906</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>3.673393865066202</v>
+        <v>0.9590003248937143</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>20.76122989635906</v>
       </c>
       <c r="F64" t="n">
-        <v>3.654267331010083</v>
+        <v>1.465515248458123</v>
       </c>
       <c r="G64" t="n">
         <v>20.76122989635906</v>
       </c>
       <c r="H64" t="n">
-        <v>4.165723776804269</v>
+        <v>0.9509816931398691</v>
       </c>
       <c r="I64" t="n">
         <v>20.76122989635906</v>
       </c>
       <c r="J64" t="n">
-        <v>4.095997196781624</v>
+        <v>1.465456029896142</v>
       </c>
       <c r="K64" t="n">
         <v>20.76122989635906</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>5.287231657118586</v>
+        <v>2.204788683918402</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>20.76122989635906</v>
       </c>
       <c r="F65" t="n">
-        <v>5.217702689972353</v>
+        <v>2.593433819905538</v>
       </c>
       <c r="G65" t="n">
         <v>20.76122989635906</v>
       </c>
       <c r="H65" t="n">
-        <v>5.494043452638859</v>
+        <v>2.184511777217242</v>
       </c>
       <c r="I65" t="n">
         <v>20.76122989635906</v>
       </c>
       <c r="J65" t="n">
-        <v>5.441667769438239</v>
+        <v>2.598004271179253</v>
       </c>
       <c r="K65" t="n">
         <v>20.76122989635906</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>6.098772927612337</v>
+        <v>2.204788683918402</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>20.76122989635906</v>
       </c>
       <c r="F66" t="n">
-        <v>6.049126185236013</v>
+        <v>2.593433819905534</v>
       </c>
       <c r="G66" t="n">
         <v>20.76122989635906</v>
       </c>
       <c r="H66" t="n">
-        <v>6.309761036315173</v>
+        <v>2.184511777217242</v>
       </c>
       <c r="I66" t="n">
         <v>20.76122989635906</v>
       </c>
       <c r="J66" t="n">
-        <v>6.273091264701898</v>
+        <v>2.598004271179253</v>
       </c>
       <c r="K66" t="n">
         <v>20.76122989635906</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.6425399635127058</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.6425399635127058</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9951351671921304</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9951351671921304</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.227589192888331</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.227589192888331</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1.396857656047443</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1.396857656047443</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.527884536509158</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1.527884536509158</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="77">
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.6425399635127058</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.6425399635127058</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="78">
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9951351671921304</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9951351671921304</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="79">
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.227589192888331</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1.227589192888331</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="80">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.396857656047443</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1.396857656047443</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1.527884536509158</v>
+        <v>20.76122989635906</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1.527884536509158</v>
+        <v>20.76122989635906</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
